--- a/Documentation/Reports and Papers/Knee_Torque_Test/Tables/CoefficientTable.xlsx
+++ b/Documentation/Reports and Papers/Knee_Torque_Test/Tables/CoefficientTable.xlsx
@@ -8,17 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Bipedal_Robot\Documentation\Reports and Papers\Knee_Torque_Test\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9681CAAB-AC71-4ED6-BFAA-34B9FFFC9CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B141018B-DEF6-4AD6-84B6-E18E64201F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gof_FlxExt" sheetId="5" r:id="rId1"/>
     <sheet name="Optimized values" sheetId="6" r:id="rId2"/>
     <sheet name="FlxPin" sheetId="7" r:id="rId3"/>
     <sheet name="FlxBio" sheetId="8" r:id="rId4"/>
+    <sheet name="ExtPin" sheetId="10" r:id="rId5"/>
+    <sheet name="ExtBio" sheetId="12" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="30">
   <si>
     <t>RMSE</t>
   </si>
@@ -101,23 +104,41 @@
     <t>Max. Residual</t>
   </si>
   <si>
-    <t>$l_rest=\qty{48.0}{\cm}$</t>
-  </si>
-  <si>
-    <t>$l_rest=\qty{45.7}{\cm}$</t>
-  </si>
-  <si>
     <t>$\phi$\qty{10}{\mm}</t>
   </si>
   <si>
     <t>$\phi$\qty{20}{\mm}</t>
+  </si>
+  <si>
+    <t>$l_0=\qty{48.0}{\cm}$</t>
+  </si>
+  <si>
+    <t>$l_0=\qty{45.7}{\cm}$</t>
+  </si>
+  <si>
+    <t>Absolute reduction</t>
+  </si>
+  <si>
+    <t>Relative reduction</t>
+  </si>
+  <si>
+    <t>Final proportion</t>
+  </si>
+  <si>
+    <t>Fold improvement</t>
+  </si>
+  <si>
+    <t>}</t>
+  </si>
+  <si>
+    <t>Mean improvement</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -143,6 +164,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="36"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -184,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -201,12 +229,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,14 +530,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="12" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="9" t="s">
@@ -519,10 +552,10 @@
       <c r="J1" s="9"/>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
       <c r="E2" s="4" t="s">
         <v>9</v>
       </c>
@@ -543,10 +576,10 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2">
@@ -575,8 +608,8 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="2">
         <v>10</v>
       </c>
@@ -603,8 +636,8 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12" t="s">
+      <c r="A5" s="10"/>
+      <c r="B5" s="11" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="2">
@@ -633,8 +666,8 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="11"/>
       <c r="C6" s="2">
         <v>20</v>
       </c>
@@ -661,7 +694,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="10" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="9" t="s">
@@ -693,7 +726,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="11"/>
+      <c r="A8" s="10"/>
       <c r="B8" s="9"/>
       <c r="C8" s="2">
         <v>10</v>
@@ -721,7 +754,7 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="11"/>
+      <c r="A9" s="10"/>
       <c r="B9" s="9"/>
       <c r="C9" s="2">
         <v>10</v>
@@ -749,7 +782,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
+      <c r="A10" s="10"/>
       <c r="B10" s="3" t="s">
         <v>3</v>
       </c>
@@ -780,16 +813,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="A7:A10"/>
     <mergeCell ref="A3:A6"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -860,22 +893,29 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13494F01-D57D-450A-B763-813D8766D7FF}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="12" max="12" width="16.85546875" customWidth="1"/>
+    <col min="13" max="13" width="10.85546875" customWidth="1"/>
+    <col min="15" max="15" width="19.42578125" customWidth="1"/>
+    <col min="16" max="16" width="17.5703125" customWidth="1"/>
+    <col min="17" max="17" width="15.42578125" customWidth="1"/>
+    <col min="18" max="18" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -895,7 +935,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
@@ -917,8 +957,29 @@
       <c r="G3">
         <v>6.7526000000000002</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="L3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -940,8 +1001,196 @@
       <c r="G4">
         <v>4.6946000000000003</v>
       </c>
+      <c r="J4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>4.8705999999999996</v>
+      </c>
+      <c r="M4">
+        <v>1.6074999999999999</v>
+      </c>
+      <c r="O4">
+        <f>L4-M4</f>
+        <v>3.2630999999999997</v>
+      </c>
+      <c r="P4" s="13">
+        <f>O4/L4</f>
+        <v>0.66995852667022537</v>
+      </c>
+      <c r="Q4" s="13">
+        <f>M4/L4</f>
+        <v>0.33004147332977457</v>
+      </c>
+      <c r="R4" s="14">
+        <f>L4/M4</f>
+        <v>3.0299222395023326</v>
+      </c>
+      <c r="S4" s="15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="K5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L5">
+        <v>0.72330000000000005</v>
+      </c>
+      <c r="M5">
+        <v>9.4799999999999995E-2</v>
+      </c>
+      <c r="O5">
+        <f t="shared" ref="O5:O9" si="0">L5-M5</f>
+        <v>0.62850000000000006</v>
+      </c>
+      <c r="P5" s="13">
+        <f t="shared" ref="P5:P9" si="1">O5/L5</f>
+        <v>0.86893405226047282</v>
+      </c>
+      <c r="Q5" s="13">
+        <f t="shared" ref="Q5:Q9" si="2">M5/L5</f>
+        <v>0.13106594773952715</v>
+      </c>
+      <c r="R5" s="14">
+        <f t="shared" ref="R5:R9" si="3">L5/M5</f>
+        <v>7.6297468354430391</v>
+      </c>
+      <c r="S5" s="15"/>
+      <c r="T5" s="14">
+        <f>AVERAGE(R4:R6)</f>
+        <v>4.567462766712973</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="K6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6">
+        <v>9.8648000000000007</v>
+      </c>
+      <c r="M6">
+        <v>3.2421000000000002</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="0"/>
+        <v>6.6227</v>
+      </c>
+      <c r="P6" s="13">
+        <f t="shared" si="1"/>
+        <v>0.67134660611467034</v>
+      </c>
+      <c r="Q6" s="13">
+        <f t="shared" si="2"/>
+        <v>0.32865339388532966</v>
+      </c>
+      <c r="R6" s="14">
+        <f t="shared" si="3"/>
+        <v>3.0427192251935473</v>
+      </c>
+      <c r="S6" s="15"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="J7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>3.0238999999999998</v>
+      </c>
+      <c r="M7">
+        <v>1.9151</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="0"/>
+        <v>1.1087999999999998</v>
+      </c>
+      <c r="P7" s="13">
+        <f t="shared" si="1"/>
+        <v>0.36667879228810474</v>
+      </c>
+      <c r="Q7" s="13">
+        <f t="shared" si="2"/>
+        <v>0.63332120771189526</v>
+      </c>
+      <c r="R7" s="14">
+        <f t="shared" si="3"/>
+        <v>1.5789775990809878</v>
+      </c>
+      <c r="S7" s="15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="K8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L8">
+        <v>0.16320000000000001</v>
+      </c>
+      <c r="M8">
+        <v>7.1599999999999997E-2</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="0"/>
+        <v>9.1600000000000015E-2</v>
+      </c>
+      <c r="P8" s="13">
+        <f t="shared" si="1"/>
+        <v>0.56127450980392157</v>
+      </c>
+      <c r="Q8" s="13">
+        <f t="shared" si="2"/>
+        <v>0.43872549019607837</v>
+      </c>
+      <c r="R8" s="14">
+        <f t="shared" si="3"/>
+        <v>2.2793296089385477</v>
+      </c>
+      <c r="S8" s="15"/>
+      <c r="T8" s="14">
+        <f>AVERAGE(R7:R9)</f>
+        <v>1.7655610714983536</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="K9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L9">
+        <v>6.7526000000000002</v>
+      </c>
+      <c r="M9">
+        <v>4.6946000000000003</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="0"/>
+        <v>2.0579999999999998</v>
+      </c>
+      <c r="P9" s="13">
+        <f t="shared" si="1"/>
+        <v>0.3047714954239848</v>
+      </c>
+      <c r="Q9" s="13">
+        <f t="shared" si="2"/>
+        <v>0.69522850457601515</v>
+      </c>
+      <c r="R9" s="14">
+        <f t="shared" si="3"/>
+        <v>1.4383760064755251</v>
+      </c>
+      <c r="S9" s="15"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="S4:S6"/>
+    <mergeCell ref="S7:S9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -949,22 +1198,331 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E415953-A445-45E6-AC52-8D43A9DEB943}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="16" max="16" width="17.85546875" customWidth="1"/>
+    <col min="17" max="17" width="17.7109375" customWidth="1"/>
+    <col min="18" max="18" width="16.140625" customWidth="1"/>
+    <col min="19" max="19" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
+        <v>7.4481999999999999</v>
+      </c>
+      <c r="C3">
+        <v>5.5566000000000004</v>
+      </c>
+      <c r="D3">
+        <v>13.308400000000001</v>
+      </c>
+      <c r="E3">
+        <v>14.8028</v>
+      </c>
+      <c r="F3">
+        <v>3.3656000000000001</v>
+      </c>
+      <c r="G3">
+        <v>23.714700000000001</v>
+      </c>
+      <c r="K3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>7.4481999999999999</v>
+      </c>
+      <c r="N3">
+        <v>0.68030000000000002</v>
+      </c>
+      <c r="P3">
+        <f>M3-N3</f>
+        <v>6.7679</v>
+      </c>
+      <c r="Q3" s="13">
+        <f>P3/M3</f>
+        <v>0.90866249563652968</v>
+      </c>
+      <c r="R3" s="13">
+        <f>N3/M3</f>
+        <v>9.1337504363470365E-2</v>
+      </c>
+      <c r="S3" s="14">
+        <f>M3/N3</f>
+        <v>10.948405115390269</v>
+      </c>
+      <c r="T3" s="15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4">
+        <v>0.68030000000000002</v>
+      </c>
+      <c r="C4">
+        <v>5.2200000000000003E-2</v>
+      </c>
+      <c r="D4">
+        <v>1.0546</v>
+      </c>
+      <c r="E4">
+        <v>2.8675999999999999</v>
+      </c>
+      <c r="F4">
+        <v>0.1263</v>
+      </c>
+      <c r="G4">
+        <v>3.5497999999999998</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4">
+        <v>5.5566000000000004</v>
+      </c>
+      <c r="N4">
+        <v>5.2200000000000003E-2</v>
+      </c>
+      <c r="P4">
+        <f t="shared" ref="P4:P8" si="0">M4-N4</f>
+        <v>5.5044000000000004</v>
+      </c>
+      <c r="Q4" s="13">
+        <f t="shared" ref="Q4:Q8" si="1">P4/M4</f>
+        <v>0.99060576611597018</v>
+      </c>
+      <c r="R4" s="13">
+        <f t="shared" ref="R4:R8" si="2">N4/M4</f>
+        <v>9.3942338840298026E-3</v>
+      </c>
+      <c r="S4" s="14">
+        <f t="shared" ref="S4:S8" si="3">M4/N4</f>
+        <v>106.44827586206897</v>
+      </c>
+      <c r="T4" s="15"/>
+      <c r="U4" s="14">
+        <f>AVERAGE(S3:S5)</f>
+        <v>43.33868757785843</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="L5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M5">
+        <v>13.308400000000001</v>
+      </c>
+      <c r="N5">
+        <v>1.0546</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="0"/>
+        <v>12.2538</v>
+      </c>
+      <c r="Q5" s="13">
+        <f t="shared" si="1"/>
+        <v>0.92075681524450714</v>
+      </c>
+      <c r="R5" s="13">
+        <f t="shared" si="2"/>
+        <v>7.924318475549276E-2</v>
+      </c>
+      <c r="S5" s="14">
+        <f t="shared" si="3"/>
+        <v>12.619381756116065</v>
+      </c>
+      <c r="T5" s="15"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="K6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>14.8028</v>
+      </c>
+      <c r="N6">
+        <v>2.8675999999999999</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="0"/>
+        <v>11.9352</v>
+      </c>
+      <c r="Q6" s="13">
+        <f t="shared" si="1"/>
+        <v>0.80627989299321756</v>
+      </c>
+      <c r="R6" s="13">
+        <f t="shared" si="2"/>
+        <v>0.19372010700678249</v>
+      </c>
+      <c r="S6" s="14">
+        <f t="shared" si="3"/>
+        <v>5.1620867624494347</v>
+      </c>
+      <c r="T6" s="15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="L7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M7">
+        <v>3.3656000000000001</v>
+      </c>
+      <c r="N7">
+        <v>0.1263</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="0"/>
+        <v>3.2393000000000001</v>
+      </c>
+      <c r="Q7" s="13">
+        <f t="shared" si="1"/>
+        <v>0.96247325885429047</v>
+      </c>
+      <c r="R7" s="13">
+        <f t="shared" si="2"/>
+        <v>3.752674114570953E-2</v>
+      </c>
+      <c r="S7" s="14">
+        <f t="shared" si="3"/>
+        <v>26.647664291369757</v>
+      </c>
+      <c r="T7" s="15"/>
+      <c r="U7" s="14">
+        <f>AVERAGE(S6:S8)</f>
+        <v>12.830108202419607</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="L8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M8">
+        <v>23.714700000000001</v>
+      </c>
+      <c r="N8">
+        <v>3.5497999999999998</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="0"/>
+        <v>20.164899999999999</v>
+      </c>
+      <c r="Q8" s="13">
+        <f t="shared" si="1"/>
+        <v>0.85031225358111207</v>
+      </c>
+      <c r="R8" s="13">
+        <f t="shared" si="2"/>
+        <v>0.14968774641888785</v>
+      </c>
+      <c r="S8" s="14">
+        <f t="shared" si="3"/>
+        <v>6.6805735534396309</v>
+      </c>
+      <c r="T8" s="15"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="T3:T5"/>
+    <mergeCell ref="T6:T8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BD037EE-E1A1-433C-A584-5AF81DBAEE85}">
+  <dimension ref="A1:W12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" customWidth="1"/>
+    <col min="18" max="18" width="19.85546875" customWidth="1"/>
+    <col min="19" max="19" width="18" customWidth="1"/>
+    <col min="20" max="20" width="15.42578125" customWidth="1"/>
+    <col min="21" max="21" width="17.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>22</v>
       </c>
       <c r="F1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -983,54 +1541,588 @@
       <c r="G2" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B3">
-        <v>7.4481999999999999</v>
+        <v>4.8705999999999996</v>
       </c>
       <c r="C3">
-        <v>5.5566000000000004</v>
+        <v>0.72330000000000005</v>
       </c>
       <c r="D3">
-        <v>13.308400000000001</v>
+        <v>9.8648000000000007</v>
       </c>
       <c r="E3">
-        <v>14.8028</v>
+        <v>3.0238999999999998</v>
       </c>
       <c r="F3">
-        <v>3.3656000000000001</v>
+        <v>0.16320000000000001</v>
       </c>
       <c r="G3">
-        <v>23.714700000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>6.7526000000000002</v>
+      </c>
+      <c r="H3">
+        <v>3.0238999999999998</v>
+      </c>
+      <c r="I3">
+        <v>0.16320000000000001</v>
+      </c>
+      <c r="J3">
+        <v>6.7526000000000002</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B4">
-        <v>0.68030000000000002</v>
+        <v>1.6074999999999999</v>
       </c>
       <c r="C4">
-        <v>5.2200000000000003E-2</v>
+        <v>9.4799999999999995E-2</v>
       </c>
       <c r="D4">
-        <v>1.0546</v>
+        <v>3.2421000000000002</v>
       </c>
       <c r="E4">
-        <v>2.8675999999999999</v>
+        <v>1.9151</v>
       </c>
       <c r="F4">
-        <v>0.1263</v>
+        <v>7.1599999999999997E-2</v>
       </c>
       <c r="G4">
-        <v>3.5497999999999998</v>
-      </c>
+        <v>4.6946000000000003</v>
+      </c>
+      <c r="H4">
+        <v>1.9151</v>
+      </c>
+      <c r="I4">
+        <v>7.1599999999999997E-2</v>
+      </c>
+      <c r="J4">
+        <v>4.6946000000000003</v>
+      </c>
+      <c r="M4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>4.8705999999999996</v>
+      </c>
+      <c r="P4">
+        <v>1.6074999999999999</v>
+      </c>
+      <c r="R4">
+        <f>O4-P4</f>
+        <v>3.2630999999999997</v>
+      </c>
+      <c r="S4" s="13">
+        <f>R4/O4</f>
+        <v>0.66995852667022537</v>
+      </c>
+      <c r="T4" s="13">
+        <f>P4/O4</f>
+        <v>0.33004147332977457</v>
+      </c>
+      <c r="U4" s="14">
+        <f>O4/P4</f>
+        <v>3.0299222395023326</v>
+      </c>
+      <c r="V4" s="15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O5">
+        <v>0.72330000000000005</v>
+      </c>
+      <c r="P5">
+        <v>9.4799999999999995E-2</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R12" si="0">O5-P5</f>
+        <v>0.62850000000000006</v>
+      </c>
+      <c r="S5" s="13">
+        <f t="shared" ref="S5:S12" si="1">R5/O5</f>
+        <v>0.86893405226047282</v>
+      </c>
+      <c r="T5" s="13">
+        <f t="shared" ref="T5:T12" si="2">P5/O5</f>
+        <v>0.13106594773952715</v>
+      </c>
+      <c r="U5" s="14">
+        <f t="shared" ref="U5:U12" si="3">O5/P5</f>
+        <v>7.6297468354430391</v>
+      </c>
+      <c r="V5" s="15"/>
+      <c r="W5" s="14">
+        <f>AVERAGE(U4:U6)</f>
+        <v>4.567462766712973</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6">
+        <v>9.8648000000000007</v>
+      </c>
+      <c r="P6">
+        <v>3.2421000000000002</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="0"/>
+        <v>6.6227</v>
+      </c>
+      <c r="S6" s="13">
+        <f t="shared" si="1"/>
+        <v>0.67134660611467034</v>
+      </c>
+      <c r="T6" s="13">
+        <f t="shared" si="2"/>
+        <v>0.32865339388532966</v>
+      </c>
+      <c r="U6" s="14">
+        <f t="shared" si="3"/>
+        <v>3.0427192251935473</v>
+      </c>
+      <c r="V6" s="15"/>
+    </row>
+    <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>3.0238999999999998</v>
+      </c>
+      <c r="P7">
+        <v>1.9151</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="0"/>
+        <v>1.1087999999999998</v>
+      </c>
+      <c r="S7" s="13">
+        <f t="shared" si="1"/>
+        <v>0.36667879228810474</v>
+      </c>
+      <c r="T7" s="13">
+        <f t="shared" si="2"/>
+        <v>0.63332120771189526</v>
+      </c>
+      <c r="U7" s="14">
+        <f t="shared" si="3"/>
+        <v>1.5789775990809878</v>
+      </c>
+      <c r="V7" s="15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O8">
+        <v>0.16320000000000001</v>
+      </c>
+      <c r="P8">
+        <v>7.1599999999999997E-2</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="0"/>
+        <v>9.1600000000000015E-2</v>
+      </c>
+      <c r="S8" s="13">
+        <f t="shared" si="1"/>
+        <v>0.56127450980392157</v>
+      </c>
+      <c r="T8" s="13">
+        <f t="shared" si="2"/>
+        <v>0.43872549019607837</v>
+      </c>
+      <c r="U8" s="14">
+        <f t="shared" si="3"/>
+        <v>2.2793296089385477</v>
+      </c>
+      <c r="V8" s="15"/>
+      <c r="W8" s="14">
+        <f>AVERAGE(U7:U9)</f>
+        <v>1.7655610714983536</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9">
+        <v>6.7526000000000002</v>
+      </c>
+      <c r="P9">
+        <v>4.6946000000000003</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="0"/>
+        <v>2.0579999999999998</v>
+      </c>
+      <c r="S9" s="13">
+        <f t="shared" si="1"/>
+        <v>0.3047714954239848</v>
+      </c>
+      <c r="T9" s="13">
+        <f t="shared" si="2"/>
+        <v>0.69522850457601515</v>
+      </c>
+      <c r="U9" s="14">
+        <f t="shared" si="3"/>
+        <v>1.4383760064755251</v>
+      </c>
+      <c r="V9" s="15"/>
+    </row>
+    <row r="10" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>3.0238999999999998</v>
+      </c>
+      <c r="P10">
+        <v>1.9151</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="0"/>
+        <v>1.1087999999999998</v>
+      </c>
+      <c r="S10" s="13">
+        <f t="shared" si="1"/>
+        <v>0.36667879228810474</v>
+      </c>
+      <c r="T10" s="13">
+        <f t="shared" si="2"/>
+        <v>0.63332120771189526</v>
+      </c>
+      <c r="U10" s="14">
+        <f t="shared" si="3"/>
+        <v>1.5789775990809878</v>
+      </c>
+      <c r="V10" s="15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O11">
+        <v>0.16320000000000001</v>
+      </c>
+      <c r="P11">
+        <v>7.1599999999999997E-2</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="0"/>
+        <v>9.1600000000000015E-2</v>
+      </c>
+      <c r="S11" s="13">
+        <f t="shared" si="1"/>
+        <v>0.56127450980392157</v>
+      </c>
+      <c r="T11" s="13">
+        <f t="shared" si="2"/>
+        <v>0.43872549019607837</v>
+      </c>
+      <c r="U11" s="14">
+        <f t="shared" si="3"/>
+        <v>2.2793296089385477</v>
+      </c>
+      <c r="V11" s="15"/>
+      <c r="W11" s="14">
+        <f>AVERAGE(U10:U12)</f>
+        <v>1.7655610714983536</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12">
+        <v>6.7526000000000002</v>
+      </c>
+      <c r="P12">
+        <v>4.6946000000000003</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="0"/>
+        <v>2.0579999999999998</v>
+      </c>
+      <c r="S12" s="13">
+        <f t="shared" si="1"/>
+        <v>0.3047714954239848</v>
+      </c>
+      <c r="T12" s="13">
+        <f t="shared" si="2"/>
+        <v>0.69522850457601515</v>
+      </c>
+      <c r="U12" s="14">
+        <f t="shared" si="3"/>
+        <v>1.4383760064755251</v>
+      </c>
+      <c r="V12" s="15"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="V4:V6"/>
+    <mergeCell ref="V7:V9"/>
+    <mergeCell ref="V10:V12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{970EC6D9-1B5E-4DCF-99EA-26D63720F071}">
+  <dimension ref="A1:Q9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="19.42578125" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" customWidth="1"/>
+    <col min="14" max="14" width="15.42578125" customWidth="1"/>
+    <col min="15" max="15" width="17.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
+        <v>4.8705999999999996</v>
+      </c>
+      <c r="C3">
+        <v>0.72330000000000005</v>
+      </c>
+      <c r="D3">
+        <v>9.8648000000000007</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4">
+        <v>1.6074999999999999</v>
+      </c>
+      <c r="C4">
+        <v>9.4799999999999995E-2</v>
+      </c>
+      <c r="D4">
+        <v>3.2421000000000002</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>4.8705999999999996</v>
+      </c>
+      <c r="J4">
+        <v>1.6074999999999999</v>
+      </c>
+      <c r="L4">
+        <f>I4-J4</f>
+        <v>3.2630999999999997</v>
+      </c>
+      <c r="M4" s="13">
+        <f>L4/I4</f>
+        <v>0.66995852667022537</v>
+      </c>
+      <c r="N4" s="13">
+        <f>J4/I4</f>
+        <v>0.33004147332977457</v>
+      </c>
+      <c r="O4" s="14">
+        <f>I4/J4</f>
+        <v>3.0299222395023326</v>
+      </c>
+      <c r="P4" s="15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>0.72330000000000005</v>
+      </c>
+      <c r="J5">
+        <v>9.4799999999999995E-2</v>
+      </c>
+      <c r="L5">
+        <f t="shared" ref="L5:L9" si="0">I5-J5</f>
+        <v>0.62850000000000006</v>
+      </c>
+      <c r="M5" s="13">
+        <f t="shared" ref="M5:M8" si="1">L5/I5</f>
+        <v>0.86893405226047282</v>
+      </c>
+      <c r="N5" s="13">
+        <f t="shared" ref="N5:N9" si="2">J5/I5</f>
+        <v>0.13106594773952715</v>
+      </c>
+      <c r="O5" s="14">
+        <f t="shared" ref="O5:O9" si="3">I5/J5</f>
+        <v>7.6297468354430391</v>
+      </c>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="14">
+        <f>AVERAGE(O4:O6)</f>
+        <v>4.567462766712973</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6">
+        <v>9.8648000000000007</v>
+      </c>
+      <c r="J6">
+        <v>3.2421000000000002</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="0"/>
+        <v>6.6227</v>
+      </c>
+      <c r="M6" s="13">
+        <f t="shared" si="1"/>
+        <v>0.67134660611467034</v>
+      </c>
+      <c r="N6" s="13">
+        <f t="shared" si="2"/>
+        <v>0.32865339388532966</v>
+      </c>
+      <c r="O6" s="14">
+        <f t="shared" si="3"/>
+        <v>3.0427192251935473</v>
+      </c>
+      <c r="P6" s="15"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H7" s="1"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="15"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H8" s="1"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="14"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H9" s="1"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="15"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="P4:P6"/>
+    <mergeCell ref="P7:P9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
